--- a/01_analyses_states/Gujarat/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Gujarat/results/SoIB_summaries.xlsx
@@ -506,16 +506,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>41.7</v>
+        <v>41.9</v>
       </c>
       <c r="E2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -529,10 +529,10 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="E3">
-        <v>33.3</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -543,13 +543,13 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -563,7 +563,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E5">
         <v>1.4</v>
@@ -574,16 +574,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
-        <v>26.7</v>
+        <v>27.4</v>
       </c>
       <c r="E6">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -594,7 +594,7 @@
         <v>19</v>
       </c>
       <c r="C7">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -602,10 +602,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C8">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +700,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -708,7 +708,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -716,7 +716,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -745,7 +745,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -753,10 +753,10 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -764,10 +764,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C4">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -813,7 +813,7 @@
         <v>71</v>
       </c>
       <c r="C2">
-        <v>67</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="D2">
         <v>71</v>
@@ -830,7 +830,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -838,10 +838,10 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="D4">
         <v>15</v>
